--- a/Ozrit HR data/ozrit/HR/Salary/Attendence/Attendance & salary calculation for August 2025.xlsx
+++ b/Ozrit HR data/ozrit/HR/Salary/Attendence/Attendance & salary calculation for August 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pixld\Downloads\ozrit\Ozrit HR data\ozrit\HR\Salary\Attendence\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rani\Downloads\ozrit\Ozrit HR data\ozrit\HR\Salary\Attendence\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB19897-B0C7-48B4-A454-A2DBAF3F32A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236CA710-6F18-4994-AFD8-9E7DE4FE0FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -46369,12 +46369,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C70:F70"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="C65:F65"/>
-    <mergeCell ref="C66:F66"/>
-    <mergeCell ref="C67:F67"/>
-    <mergeCell ref="C68:F68"/>
     <mergeCell ref="J68:M68"/>
     <mergeCell ref="C69:F69"/>
     <mergeCell ref="D1:G1"/>
@@ -46384,6 +46378,12 @@
     <mergeCell ref="C63:F63"/>
     <mergeCell ref="C64:F64"/>
     <mergeCell ref="H64:K64"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="C65:F65"/>
+    <mergeCell ref="C66:F66"/>
+    <mergeCell ref="C67:F67"/>
+    <mergeCell ref="C68:F68"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -49913,8 +49913,7 @@
         <v>200</v>
       </c>
       <c r="M49" s="94">
-        <f t="shared" si="20"/>
-        <v>4800</v>
+        <v>3600</v>
       </c>
       <c r="N49" s="94">
         <f t="shared" si="21"/>
@@ -49922,7 +49921,7 @@
       </c>
       <c r="O49" s="94">
         <f t="shared" si="17"/>
-        <v>15400</v>
+        <v>16600</v>
       </c>
       <c r="P49" s="94">
         <f t="shared" si="18"/>
@@ -49930,18 +49929,18 @@
       </c>
       <c r="Q49" s="94">
         <f t="shared" si="19"/>
-        <v>45000</v>
+        <v>46200</v>
       </c>
       <c r="R49" s="9">
         <v>9</v>
       </c>
       <c r="S49" s="96">
         <f t="shared" si="7"/>
-        <v>1451.6129032258063</v>
+        <v>1490.3225806451612</v>
       </c>
       <c r="T49" s="97">
         <f t="shared" si="8"/>
-        <v>13064.516129032258</v>
+        <v>13412.903225806451</v>
       </c>
       <c r="U49" s="145">
         <v>13065</v>
@@ -50454,7 +50453,7 @@
       </c>
       <c r="T57" s="159">
         <f>SUM(T6:T56)</f>
-        <v>787891.64516129042</v>
+        <v>788240.0322580646</v>
       </c>
       <c r="U57" s="29">
         <f>SUM(U6:U56)</f>
